--- a/data/HCA_cluster_distribution.xlsx
+++ b/data/HCA_cluster_distribution.xlsx
@@ -438,34 +438,34 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>31</v>
+        <v>75</v>
       </c>
       <c r="C2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D2">
-        <v>48.6</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>14.9</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>31.1</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="H2">
         <v>0</v>
       </c>
       <c r="I2">
-        <v>1.4</v>
+        <v>100</v>
       </c>
       <c r="J2">
         <v>0</v>
       </c>
       <c r="K2">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -476,37 +476,37 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>66</v>
+        <v>208</v>
       </c>
       <c r="C3">
-        <v>1131</v>
+        <v>243</v>
       </c>
       <c r="D3">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>11.9</v>
+        <v>0.8</v>
       </c>
       <c r="F3">
-        <v>28.5</v>
+        <v>84.8</v>
       </c>
       <c r="G3">
-        <v>24.5</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="I3">
-        <v>16.7</v>
+        <v>11.1</v>
       </c>
       <c r="J3">
-        <v>4.5</v>
+        <v>0.4</v>
       </c>
       <c r="K3">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="L3">
-        <v>0</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -514,37 +514,37 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>41</v>
+        <v>66</v>
       </c>
       <c r="C4">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="D4">
-        <v>11.6</v>
+        <v>2</v>
       </c>
       <c r="E4">
-        <v>14.2</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>14.2</v>
+        <v>26.7</v>
       </c>
       <c r="G4">
-        <v>7.7</v>
+        <v>54.7</v>
       </c>
       <c r="H4">
-        <v>3.9</v>
+        <v>1.3</v>
       </c>
       <c r="I4">
-        <v>17.4</v>
+        <v>12.7</v>
       </c>
       <c r="J4">
-        <v>28.4</v>
+        <v>0.7</v>
       </c>
       <c r="K4">
-        <v>2.6</v>
+        <v>1.3</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -552,37 +552,37 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="C5">
-        <v>176</v>
+        <v>416</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>45.9</v>
       </c>
       <c r="F5">
-        <v>100</v>
+        <v>26.4</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -590,37 +590,37 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="C6">
-        <v>69</v>
+        <v>224</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="E6">
-        <v>100</v>
+        <v>2.2</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>18.3</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>11.2</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>53.1</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -628,37 +628,37 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>90</v>
+        <v>31</v>
       </c>
       <c r="C7">
-        <v>233</v>
+        <v>74</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>48.6</v>
       </c>
       <c r="E7">
-        <v>36.5</v>
+        <v>14.9</v>
       </c>
       <c r="F7">
-        <v>40.8</v>
+        <v>31.1</v>
       </c>
       <c r="G7">
-        <v>5.2</v>
+        <v>2.7</v>
       </c>
       <c r="H7">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="I7">
-        <v>10.3</v>
+        <v>1.4</v>
       </c>
       <c r="J7">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="K7">
-        <v>0.4</v>
+        <v>1.4</v>
       </c>
       <c r="L7">
-        <v>5.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -666,37 +666,37 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>180</v>
+        <v>68</v>
       </c>
       <c r="C8">
-        <v>384</v>
+        <v>1151</v>
       </c>
       <c r="D8">
-        <v>0.8</v>
+        <v>5.9</v>
       </c>
       <c r="E8">
-        <v>2.6</v>
+        <v>12</v>
       </c>
       <c r="F8">
-        <v>18.8</v>
+        <v>28.2</v>
       </c>
       <c r="G8">
-        <v>8.1</v>
+        <v>23.8</v>
       </c>
       <c r="H8">
-        <v>7.3</v>
+        <v>4.8</v>
       </c>
       <c r="I8">
-        <v>59.9</v>
+        <v>16.5</v>
       </c>
       <c r="J8">
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="K8">
-        <v>1.6</v>
+        <v>3.8</v>
       </c>
       <c r="L8">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -704,34 +704,34 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="C9">
-        <v>158</v>
+        <v>47</v>
       </c>
       <c r="D9">
-        <v>1.9</v>
+        <v>12.8</v>
       </c>
       <c r="E9">
-        <v>10.8</v>
+        <v>4.3</v>
       </c>
       <c r="F9">
-        <v>22.8</v>
+        <v>2.1</v>
       </c>
       <c r="G9">
-        <v>54.4</v>
+        <v>12.8</v>
       </c>
       <c r="H9">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="I9">
-        <v>3.2</v>
+        <v>17</v>
       </c>
       <c r="J9">
-        <v>0.6</v>
+        <v>42.6</v>
       </c>
       <c r="K9">
-        <v>3.2</v>
+        <v>8.5</v>
       </c>
       <c r="L9">
         <v>0</v>
